--- a/dataset/products_hasaki.xlsx
+++ b/dataset/products_hasaki.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d91abe148337f8a3/Documents/các dl làm sạch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3EB6542-E554-4946-A1D9-234BA6533396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{ED29E726-604F-4E2D-A106-A61C587E724C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D88D237-A103-42D5-94A8-44EFD0ED4D15}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{76CDC6FF-1444-408F-8309-1F50D3F77646}"/>
   </bookViews>
@@ -650,7 +650,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -665,6 +665,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1084,7 +1085,17 @@
         <v>8</v>
       </c>
       <c r="J2" t="str">
-        <f>IF(ISNUMBER(SEARCH("combo", B2)), "Combo/Set", IF(ISNUMBER(SEARCH("tẩy", B2)), "Tẩy tế bào chết", IF(ISNUMBER(SEARCH("rửa mặt", B2)), "Làm sạch mặt", IF(ISNUMBER(SEARCH("tóc", B2)), "Chăm sóc tóc", IF(ISNUMBER(SEARCH("xịt khoáng", B2)), "Toner/Xịt khoáng", "Khác")))))</f>
+        <f>IF(ISNUMBER(SEARCH("combo",B2)),"Combo/Set",
+IF(ISNUMBER(SEARCH("tẩy trang",B2)),"Tẩy trang",
+IF(OR(ISNUMBER(SEARCH("tẩy tế bào chết",B2)),ISNUMBER(SEARCH("tẩy da chết",B2))),"Tẩy tế bào chết",
+IF(ISNUMBER(SEARCH("rửa mặt",B2)),"Làm sạch mặt",
+IF(OR(ISNUMBER(SEARCH("gội",B2)),ISNUMBER(SEARCH("xả",B2)),ISNUMBER(SEARCH("tóc",B2))),"Chăm sóc tóc",
+IF(ISNUMBER(SEARCH("son dưỡng",B2)),"Chăm sóc môi",
+IF(ISNUMBER(SEARCH("chống nắng",B2)),"Chống nắng",
+IF(ISNUMBER(SEARCH("mặt nạ",B2)),"Mặt nạ",
+IF(OR(ISNUMBER(SEARCH("xịt khoáng",B2)),ISNUMBER(SEARCH("nước hoa hồng",B2)),ISNUMBER(SEARCH("nước cân bằng",B2))),"Toner/Xịt khoáng",
+IF(OR(ISNUMBER(SEARCH("tinh chất",B2)),ISNUMBER(SEARCH("kem dưỡng",B2))),"Serum/Dưỡng da",
+IF(OR(ISNUMBER(SEARCH("gel tắm",B2)),ISNUMBER(SEARCH("thâm mụn lưng",B2))),"Chăm sóc body","Khác")))))))))))</f>
         <v>Chăm sóc tóc</v>
       </c>
       <c r="K2" t="str">
@@ -1095,9 +1106,9 @@
         <f xml:space="preserve"> D2 * E2</f>
         <v>2674000</v>
       </c>
-      <c r="M2" s="4">
-        <f xml:space="preserve"> MAX(0, ROUND((1 - (F2 / L2)) * 100, 2))</f>
-        <v>28.05</v>
+      <c r="M2" s="8">
+        <f>IF(D2&gt;C2, (D2-C2)/D2, 0)</f>
+        <v>0.24083769633507854</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1129,7 +1140,17 @@
         <v>10</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J66" si="0">IF(ISNUMBER(SEARCH("combo", B3)), "Combo/Set", IF(ISNUMBER(SEARCH("tẩy", B3)), "Tẩy tế bào chết", IF(ISNUMBER(SEARCH("rửa mặt", B3)), "Làm sạch mặt", IF(ISNUMBER(SEARCH("tóc", B3)), "Chăm sóc tóc", IF(ISNUMBER(SEARCH("xịt khoáng", B3)), "Toner/Xịt khoáng", "Khác")))))</f>
+        <f t="shared" ref="J3:J66" si="0">IF(ISNUMBER(SEARCH("combo",B3)),"Combo/Set",
+IF(ISNUMBER(SEARCH("tẩy trang",B3)),"Tẩy trang",
+IF(OR(ISNUMBER(SEARCH("tẩy tế bào chết",B3)),ISNUMBER(SEARCH("tẩy da chết",B3))),"Tẩy tế bào chết",
+IF(ISNUMBER(SEARCH("rửa mặt",B3)),"Làm sạch mặt",
+IF(OR(ISNUMBER(SEARCH("gội",B3)),ISNUMBER(SEARCH("xả",B3)),ISNUMBER(SEARCH("tóc",B3))),"Chăm sóc tóc",
+IF(ISNUMBER(SEARCH("son dưỡng",B3)),"Chăm sóc môi",
+IF(ISNUMBER(SEARCH("chống nắng",B3)),"Chống nắng",
+IF(ISNUMBER(SEARCH("mặt nạ",B3)),"Mặt nạ",
+IF(OR(ISNUMBER(SEARCH("xịt khoáng",B3)),ISNUMBER(SEARCH("nước hoa hồng",B3)),ISNUMBER(SEARCH("nước cân bằng",B3))),"Toner/Xịt khoáng",
+IF(OR(ISNUMBER(SEARCH("tinh chất",B3)),ISNUMBER(SEARCH("kem dưỡng",B3))),"Serum/Dưỡng da",
+IF(OR(ISNUMBER(SEARCH("gel tắm",B3)),ISNUMBER(SEARCH("thâm mụn lưng",B3))),"Chăm sóc body","Khác")))))))))))</f>
         <v>Tẩy tế bào chết</v>
       </c>
       <c r="K3" t="str">
@@ -1140,9 +1161,9 @@
         <f t="shared" ref="L3:L66" si="2" xml:space="preserve"> D3 * E3</f>
         <v>17556000</v>
       </c>
-      <c r="M3" s="4">
-        <f t="shared" ref="M3:M66" si="3" xml:space="preserve"> MAX(0, ROUND((1 - (F3 / L3)) * 100, 2))</f>
-        <v>28.63</v>
+      <c r="M3" s="8">
+        <f t="shared" ref="M3:M66" si="3">IF(D3&gt;C3, (D3-C3)/D3, 0)</f>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1175,7 +1196,7 @@
       </c>
       <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Mặt nạ</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="1"/>
@@ -1185,9 +1206,9 @@
         <f t="shared" si="2"/>
         <v>10336000</v>
       </c>
-      <c r="M4" s="4">
-        <f t="shared" si="3"/>
-        <v>24.77</v>
+      <c r="M4" s="8">
+        <f t="shared" si="3"/>
+        <v>0.24342105263157895</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1220,7 +1241,7 @@
       </c>
       <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chăm sóc môi</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="1"/>
@@ -1230,9 +1251,9 @@
         <f t="shared" si="2"/>
         <v>17024000</v>
       </c>
-      <c r="M5" s="4">
-        <f t="shared" si="3"/>
-        <v>25.02</v>
+      <c r="M5" s="8">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1265,7 +1286,7 @@
       </c>
       <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>Tẩy tế bào chết</v>
+        <v>Tẩy trang</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="1"/>
@@ -1275,9 +1296,9 @@
         <f t="shared" si="2"/>
         <v>18900000</v>
       </c>
-      <c r="M6" s="4">
-        <f t="shared" si="3"/>
-        <v>34.31</v>
+      <c r="M6" s="8">
+        <f t="shared" si="3"/>
+        <v>0.33888888888888891</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1310,7 +1331,7 @@
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Serum/Dưỡng da</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="1"/>
@@ -1320,9 +1341,9 @@
         <f t="shared" si="2"/>
         <v>14625000</v>
       </c>
-      <c r="M7" s="4">
-        <f t="shared" si="3"/>
-        <v>25.79</v>
+      <c r="M7" s="8">
+        <f t="shared" si="3"/>
+        <v>0.25641025641025639</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1365,9 +1386,9 @@
         <f t="shared" si="2"/>
         <v>7500000</v>
       </c>
-      <c r="M8" s="4">
-        <f t="shared" si="3"/>
-        <v>21.6</v>
+      <c r="M8" s="8">
+        <f t="shared" si="3"/>
+        <v>0.21333333333333335</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1400,7 +1421,7 @@
       </c>
       <c r="J9" t="str">
         <f t="shared" si="0"/>
-        <v>Tẩy tế bào chết</v>
+        <v>Tẩy trang</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
@@ -1410,9 +1431,9 @@
         <f t="shared" si="2"/>
         <v>136045000</v>
       </c>
-      <c r="M9" s="4">
-        <f t="shared" si="3"/>
-        <v>34.909999999999997</v>
+      <c r="M9" s="8">
+        <f t="shared" si="3"/>
+        <v>0.34782608695652173</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1455,9 +1476,9 @@
         <f t="shared" si="2"/>
         <v>56760000</v>
       </c>
-      <c r="M10" s="4">
-        <f t="shared" si="3"/>
-        <v>32.04</v>
+      <c r="M10" s="8">
+        <f t="shared" si="3"/>
+        <v>0.31976744186046513</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1500,9 +1521,9 @@
         <f t="shared" si="2"/>
         <v>41470000</v>
       </c>
-      <c r="M11" s="4">
-        <f t="shared" si="3"/>
-        <v>51.01</v>
+      <c r="M11" s="8">
+        <f t="shared" si="3"/>
+        <v>0.50689655172413794</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1545,9 +1566,9 @@
         <f t="shared" si="2"/>
         <v>1365000</v>
       </c>
-      <c r="M12" s="4">
-        <f t="shared" si="3"/>
-        <v>23.08</v>
+      <c r="M12" s="8">
+        <f t="shared" si="3"/>
+        <v>0.1641025641025641</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1580,7 +1601,7 @@
       </c>
       <c r="J13" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Serum/Dưỡng da</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
@@ -1590,9 +1611,9 @@
         <f t="shared" si="2"/>
         <v>1590000</v>
       </c>
-      <c r="M13" s="4">
-        <f t="shared" si="3"/>
-        <v>15.47</v>
+      <c r="M13" s="8">
+        <f t="shared" si="3"/>
+        <v>0.13207547169811321</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -1625,7 +1646,7 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Toner/Xịt khoáng</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
@@ -1635,9 +1656,9 @@
         <f t="shared" si="2"/>
         <v>2730000</v>
       </c>
-      <c r="M14" s="4">
-        <f t="shared" si="3"/>
-        <v>26.19</v>
+      <c r="M14" s="8">
+        <f t="shared" si="3"/>
+        <v>0.26153846153846155</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1680,9 +1701,9 @@
         <f t="shared" si="2"/>
         <v>5655000</v>
       </c>
-      <c r="M15" s="4">
-        <f t="shared" si="3"/>
-        <v>17.84</v>
+      <c r="M15" s="8">
+        <f t="shared" si="3"/>
+        <v>0.1641025641025641</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1715,7 +1736,7 @@
       </c>
       <c r="J16" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Mặt nạ</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
@@ -1725,9 +1746,9 @@
         <f t="shared" si="2"/>
         <v>39520000</v>
       </c>
-      <c r="M16" s="4">
-        <f t="shared" si="3"/>
-        <v>27.84</v>
+      <c r="M16" s="8">
+        <f t="shared" si="3"/>
+        <v>0.27631578947368424</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -1760,7 +1781,7 @@
       </c>
       <c r="J17" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Serum/Dưỡng da</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
@@ -1770,9 +1791,9 @@
         <f t="shared" si="2"/>
         <v>2925000</v>
       </c>
-      <c r="M17" s="4">
-        <f t="shared" si="3"/>
-        <v>28</v>
+      <c r="M17" s="8">
+        <f t="shared" si="3"/>
+        <v>0.20923076923076922</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1815,9 +1836,9 @@
         <f t="shared" si="2"/>
         <v>43056000</v>
       </c>
-      <c r="M18" s="4">
-        <f t="shared" si="3"/>
-        <v>38.799999999999997</v>
+      <c r="M18" s="8">
+        <f t="shared" si="3"/>
+        <v>0.38461538461538464</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1850,7 +1871,7 @@
       </c>
       <c r="J19" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Toner/Xịt khoáng</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="1"/>
@@ -1860,9 +1881,9 @@
         <f t="shared" si="2"/>
         <v>14651000</v>
       </c>
-      <c r="M19" s="4">
-        <f t="shared" si="3"/>
-        <v>25.15</v>
+      <c r="M19" s="8">
+        <f t="shared" si="3"/>
+        <v>0.25083612040133779</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -1895,7 +1916,7 @@
       </c>
       <c r="J20" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Mặt nạ</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="1"/>
@@ -1905,9 +1926,9 @@
         <f t="shared" si="2"/>
         <v>11385000</v>
       </c>
-      <c r="M20" s="4">
-        <f t="shared" si="3"/>
-        <v>27.87</v>
+      <c r="M20" s="8">
+        <f t="shared" si="3"/>
+        <v>0.27536231884057971</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -1940,7 +1961,7 @@
       </c>
       <c r="J21" t="str">
         <f t="shared" si="0"/>
-        <v>Tẩy tế bào chết</v>
+        <v>Tẩy trang</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="1"/>
@@ -1950,9 +1971,9 @@
         <f t="shared" si="2"/>
         <v>10585000</v>
       </c>
-      <c r="M21" s="4">
-        <f t="shared" si="3"/>
-        <v>32.35</v>
+      <c r="M21" s="8">
+        <f t="shared" si="3"/>
+        <v>0.31724137931034485</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -1995,9 +2016,9 @@
         <f t="shared" si="2"/>
         <v>926300000</v>
       </c>
-      <c r="M22" s="4">
-        <f t="shared" si="3"/>
-        <v>58.84</v>
+      <c r="M22" s="8">
+        <f t="shared" si="3"/>
+        <v>0.58813559322033904</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -2030,7 +2051,7 @@
       </c>
       <c r="J23" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Serum/Dưỡng da</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="1"/>
@@ -2040,9 +2061,9 @@
         <f t="shared" si="2"/>
         <v>23920000</v>
       </c>
-      <c r="M23" s="4">
-        <f t="shared" si="3"/>
-        <v>30.39</v>
+      <c r="M23" s="8">
+        <f t="shared" si="3"/>
+        <v>0.30100334448160537</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -2075,7 +2096,7 @@
       </c>
       <c r="J24" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chăm sóc tóc</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="1"/>
@@ -2085,9 +2106,9 @@
         <f t="shared" si="2"/>
         <v>8190000</v>
       </c>
-      <c r="M24" s="4">
-        <f t="shared" si="3"/>
-        <v>24.58</v>
+      <c r="M24" s="8">
+        <f t="shared" si="3"/>
+        <v>0.23589743589743589</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -2120,7 +2141,7 @@
       </c>
       <c r="J25" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chăm sóc tóc</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="1"/>
@@ -2130,9 +2151,9 @@
         <f t="shared" si="2"/>
         <v>31270000</v>
       </c>
-      <c r="M25" s="4">
-        <f t="shared" si="3"/>
-        <v>32.35</v>
+      <c r="M25" s="8">
+        <f t="shared" si="3"/>
+        <v>0.32075471698113206</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -2165,7 +2186,7 @@
       </c>
       <c r="J26" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chăm sóc tóc</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="1"/>
@@ -2175,9 +2196,9 @@
         <f t="shared" si="2"/>
         <v>9030000</v>
       </c>
-      <c r="M26" s="4">
-        <f t="shared" si="3"/>
-        <v>20.239999999999998</v>
+      <c r="M26" s="8">
+        <f t="shared" si="3"/>
+        <v>0.19302325581395349</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -2220,9 +2241,9 @@
         <f t="shared" si="2"/>
         <v>60750000</v>
       </c>
-      <c r="M27" s="4">
-        <f t="shared" si="3"/>
-        <v>46.97</v>
+      <c r="M27" s="8">
+        <f t="shared" si="3"/>
+        <v>0.46800000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -2255,7 +2276,7 @@
       </c>
       <c r="J28" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Serum/Dưỡng da</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="1"/>
@@ -2265,9 +2286,9 @@
         <f t="shared" si="2"/>
         <v>9165000</v>
       </c>
-      <c r="M28" s="4">
-        <f t="shared" si="3"/>
-        <v>21.56</v>
+      <c r="M28" s="8">
+        <f t="shared" si="3"/>
+        <v>0.20512820512820512</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -2310,9 +2331,9 @@
         <f t="shared" si="2"/>
         <v>3010000</v>
       </c>
-      <c r="M29" s="4">
-        <f t="shared" si="3"/>
-        <v>22.56</v>
+      <c r="M29" s="8">
+        <f t="shared" si="3"/>
+        <v>0.21395348837209302</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -2355,9 +2376,9 @@
         <f t="shared" si="2"/>
         <v>8814000</v>
       </c>
-      <c r="M30" s="4">
-        <f t="shared" si="3"/>
-        <v>33.630000000000003</v>
+      <c r="M30" s="8">
+        <f t="shared" si="3"/>
+        <v>0.33628318584070799</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
@@ -2400,9 +2421,9 @@
         <f t="shared" si="2"/>
         <v>1650000</v>
       </c>
-      <c r="M31" s="4">
-        <f t="shared" si="3"/>
-        <v>18.55</v>
+      <c r="M31" s="8">
+        <f t="shared" si="3"/>
+        <v>0.15757575757575756</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -2445,9 +2466,9 @@
         <f t="shared" si="2"/>
         <v>7410000</v>
       </c>
-      <c r="M32" s="4">
-        <f t="shared" si="3"/>
-        <v>26.84</v>
+      <c r="M32" s="8">
+        <f t="shared" si="3"/>
+        <v>0.26666666666666666</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -2480,7 +2501,7 @@
       </c>
       <c r="J33" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Toner/Xịt khoáng</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="1"/>
@@ -2490,9 +2511,9 @@
         <f t="shared" si="2"/>
         <v>3315000</v>
       </c>
-      <c r="M33" s="4">
-        <f t="shared" si="3"/>
-        <v>28.08</v>
+      <c r="M33" s="8">
+        <f t="shared" si="3"/>
+        <v>0.25641025641025639</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -2535,9 +2556,9 @@
         <f t="shared" si="2"/>
         <v>870000</v>
       </c>
-      <c r="M34" s="4">
-        <f t="shared" si="3"/>
-        <v>30</v>
+      <c r="M34" s="8">
+        <f t="shared" si="3"/>
+        <v>0.17241379310344829</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -2580,9 +2601,9 @@
         <f t="shared" si="2"/>
         <v>2000000</v>
       </c>
-      <c r="M35" s="4">
-        <f t="shared" si="3"/>
-        <v>23.95</v>
+      <c r="M35" s="8">
+        <f t="shared" si="3"/>
+        <v>0.14799999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -2625,9 +2646,9 @@
         <f t="shared" si="2"/>
         <v>980000</v>
       </c>
-      <c r="M36" s="4">
-        <f t="shared" si="3"/>
-        <v>20</v>
+      <c r="M36" s="8">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -2670,9 +2691,9 @@
         <f t="shared" si="2"/>
         <v>24817000</v>
       </c>
-      <c r="M37" s="4">
-        <f t="shared" si="3"/>
-        <v>29.23</v>
+      <c r="M37" s="8">
+        <f t="shared" si="3"/>
+        <v>0.29096989966555181</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -2705,7 +2726,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Serum/Dưỡng da</v>
       </c>
       <c r="K38" t="str">
         <f t="shared" si="1"/>
@@ -2715,9 +2736,9 @@
         <f t="shared" si="2"/>
         <v>10230000</v>
       </c>
-      <c r="M38" s="4">
-        <f t="shared" si="3"/>
-        <v>28.14</v>
+      <c r="M38" s="8">
+        <f t="shared" si="3"/>
+        <v>0.24946236559139784</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -2760,9 +2781,9 @@
         <f t="shared" si="2"/>
         <v>144420000</v>
       </c>
-      <c r="M39" s="4">
-        <f t="shared" si="3"/>
-        <v>54.87</v>
+      <c r="M39" s="8">
+        <f t="shared" si="3"/>
+        <v>0.5482758620689655</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -2805,9 +2826,9 @@
         <f t="shared" si="2"/>
         <v>31350000</v>
       </c>
-      <c r="M40" s="4">
-        <f t="shared" si="3"/>
-        <v>51.3</v>
+      <c r="M40" s="8">
+        <f t="shared" si="3"/>
+        <v>0.50909090909090904</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -2850,9 +2871,9 @@
         <f t="shared" si="2"/>
         <v>4352000</v>
       </c>
-      <c r="M41" s="4">
-        <f t="shared" si="3"/>
-        <v>30.51</v>
+      <c r="M41" s="8">
+        <f t="shared" si="3"/>
+        <v>0.296875</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -2885,7 +2906,7 @@
       </c>
       <c r="J42" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chống nắng</v>
       </c>
       <c r="K42" t="str">
         <f t="shared" si="1"/>
@@ -2895,9 +2916,9 @@
         <f t="shared" si="2"/>
         <v>13825000</v>
       </c>
-      <c r="M42" s="4">
-        <f t="shared" si="3"/>
-        <v>31.46</v>
+      <c r="M42" s="8">
+        <f t="shared" si="3"/>
+        <v>0.29873417721518986</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
@@ -2940,9 +2961,9 @@
         <f t="shared" si="2"/>
         <v>165590000</v>
       </c>
-      <c r="M43" s="4">
-        <f t="shared" si="3"/>
-        <v>54.89</v>
+      <c r="M43" s="8">
+        <f t="shared" si="3"/>
+        <v>0.5482758620689655</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
@@ -2985,9 +3006,9 @@
         <f t="shared" si="2"/>
         <v>6880000</v>
       </c>
-      <c r="M44" s="4">
-        <f t="shared" si="3"/>
-        <v>18.36</v>
+      <c r="M44" s="8">
+        <f t="shared" si="3"/>
+        <v>0.15116279069767441</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
@@ -3030,9 +3051,9 @@
         <f t="shared" si="2"/>
         <v>1170000</v>
       </c>
-      <c r="M45" s="4">
-        <f t="shared" si="3"/>
-        <v>34.36</v>
+      <c r="M45" s="8">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
@@ -3075,9 +3096,9 @@
         <f t="shared" si="2"/>
         <v>20130000</v>
       </c>
-      <c r="M46" s="4">
-        <f t="shared" si="3"/>
-        <v>32.619999999999997</v>
+      <c r="M46" s="8">
+        <f t="shared" si="3"/>
+        <v>0.32121212121212123</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
@@ -3120,9 +3141,9 @@
         <f t="shared" si="2"/>
         <v>232980000</v>
       </c>
-      <c r="M47" s="4">
-        <f t="shared" si="3"/>
-        <v>58.24</v>
+      <c r="M47" s="8">
+        <f t="shared" si="3"/>
+        <v>0.58181818181818179</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
@@ -3165,9 +3186,9 @@
         <f t="shared" si="2"/>
         <v>310000</v>
       </c>
-      <c r="M48" s="4">
-        <f t="shared" si="3"/>
-        <v>20</v>
+      <c r="M48" s="8">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
@@ -3210,9 +3231,9 @@
         <f t="shared" si="2"/>
         <v>4945000</v>
       </c>
-      <c r="M49" s="4">
-        <f t="shared" si="3"/>
-        <v>28.23</v>
+      <c r="M49" s="8">
+        <f t="shared" si="3"/>
+        <v>0.26511627906976742</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
@@ -3255,9 +3276,9 @@
         <f t="shared" si="2"/>
         <v>9840000</v>
       </c>
-      <c r="M50" s="4">
-        <f t="shared" si="3"/>
-        <v>45.48</v>
+      <c r="M50" s="8">
+        <f t="shared" si="3"/>
+        <v>0.44390243902439025</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
@@ -3300,9 +3321,9 @@
         <f t="shared" si="2"/>
         <v>4875000</v>
       </c>
-      <c r="M51" s="4">
-        <f t="shared" si="3"/>
-        <v>22.99</v>
+      <c r="M51" s="8">
+        <f t="shared" si="3"/>
+        <v>0.20307692307692307</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
@@ -3345,9 +3366,9 @@
         <f t="shared" si="2"/>
         <v>630710000</v>
       </c>
-      <c r="M52" s="4">
-        <f t="shared" si="3"/>
-        <v>58.98</v>
+      <c r="M52" s="8">
+        <f t="shared" si="3"/>
+        <v>0.5898305084745763</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
@@ -3390,9 +3411,9 @@
         <f t="shared" si="2"/>
         <v>3540000</v>
       </c>
-      <c r="M53" s="4">
-        <f t="shared" si="3"/>
-        <v>26.86</v>
+      <c r="M53" s="8">
+        <f t="shared" si="3"/>
+        <v>0.15084745762711865</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
@@ -3435,9 +3456,9 @@
         <f t="shared" si="2"/>
         <v>9120000</v>
       </c>
-      <c r="M54" s="4">
-        <f t="shared" si="3"/>
-        <v>50.88</v>
+      <c r="M54" s="8">
+        <f t="shared" si="3"/>
+        <v>0.48245614035087719</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
@@ -3480,9 +3501,9 @@
         <f t="shared" si="2"/>
         <v>146150000</v>
       </c>
-      <c r="M55" s="4">
-        <f t="shared" si="3"/>
-        <v>52.36</v>
+      <c r="M55" s="8">
+        <f t="shared" si="3"/>
+        <v>0.52151898734177216</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
@@ -3515,7 +3536,7 @@
       </c>
       <c r="J56" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chăm sóc tóc</v>
       </c>
       <c r="K56" t="str">
         <f t="shared" si="1"/>
@@ -3525,9 +3546,9 @@
         <f t="shared" si="2"/>
         <v>40685000</v>
       </c>
-      <c r="M56" s="4">
-        <f t="shared" si="3"/>
-        <v>33.020000000000003</v>
+      <c r="M56" s="8">
+        <f t="shared" si="3"/>
+        <v>0.32911392405063289</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
@@ -3560,7 +3581,7 @@
       </c>
       <c r="J57" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chăm sóc tóc</v>
       </c>
       <c r="K57" t="str">
         <f t="shared" si="1"/>
@@ -3570,9 +3591,9 @@
         <f t="shared" si="2"/>
         <v>451920000</v>
       </c>
-      <c r="M57" s="4">
-        <f t="shared" si="3"/>
-        <v>42.7</v>
+      <c r="M57" s="8">
+        <f t="shared" si="3"/>
+        <v>0.42678571428571427</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
@@ -3605,7 +3626,7 @@
       </c>
       <c r="J58" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chống nắng</v>
       </c>
       <c r="K58" t="str">
         <f t="shared" si="1"/>
@@ -3615,9 +3636,9 @@
         <f t="shared" si="2"/>
         <v>12731000</v>
       </c>
-      <c r="M58" s="4">
-        <f t="shared" si="3"/>
-        <v>32.04</v>
+      <c r="M58" s="8">
+        <f t="shared" si="3"/>
+        <v>0.3120728929384966</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
@@ -3660,9 +3681,9 @@
         <f t="shared" si="2"/>
         <v>9440000</v>
       </c>
-      <c r="M59" s="4">
-        <f t="shared" si="3"/>
-        <v>55.93</v>
+      <c r="M59" s="8">
+        <f t="shared" si="3"/>
+        <v>0.55762711864406778</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
@@ -3705,9 +3726,9 @@
         <f t="shared" si="2"/>
         <v>14500000</v>
       </c>
-      <c r="M60" s="4">
-        <f t="shared" si="3"/>
-        <v>15.03</v>
+      <c r="M60" s="8">
+        <f t="shared" si="3"/>
+        <v>0.1503448275862069</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
@@ -3750,9 +3771,9 @@
         <f t="shared" si="2"/>
         <v>22750000</v>
       </c>
-      <c r="M61" s="4">
-        <f t="shared" si="3"/>
-        <v>49.12</v>
+      <c r="M61" s="8">
+        <f t="shared" si="3"/>
+        <v>0.48923076923076925</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
@@ -3795,9 +3816,9 @@
         <f t="shared" si="2"/>
         <v>67850000</v>
       </c>
-      <c r="M62" s="4">
-        <f t="shared" si="3"/>
-        <v>58.7</v>
+      <c r="M62" s="8">
+        <f t="shared" si="3"/>
+        <v>0.58644067796610166</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
@@ -3830,7 +3851,7 @@
       </c>
       <c r="J63" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Chăm sóc tóc</v>
       </c>
       <c r="K63" t="str">
         <f t="shared" si="1"/>
@@ -3840,9 +3861,9 @@
         <f t="shared" si="2"/>
         <v>6375000</v>
       </c>
-      <c r="M63" s="4">
-        <f t="shared" si="3"/>
-        <v>35.15</v>
+      <c r="M63" s="8">
+        <f t="shared" si="3"/>
+        <v>0.31466666666666665</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
@@ -3875,7 +3896,7 @@
       </c>
       <c r="J64" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Toner/Xịt khoáng</v>
       </c>
       <c r="K64" t="str">
         <f t="shared" si="1"/>
@@ -3885,9 +3906,9 @@
         <f t="shared" si="2"/>
         <v>12675000</v>
       </c>
-      <c r="M64" s="4">
-        <f t="shared" si="3"/>
-        <v>42.72</v>
+      <c r="M64" s="8">
+        <f t="shared" si="3"/>
+        <v>0.42564102564102563</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
@@ -3920,7 +3941,7 @@
       </c>
       <c r="J65" t="str">
         <f t="shared" si="0"/>
-        <v>Khác</v>
+        <v>Toner/Xịt khoáng</v>
       </c>
       <c r="K65" t="str">
         <f t="shared" si="1"/>
@@ -3930,9 +3951,9 @@
         <f t="shared" si="2"/>
         <v>43056000</v>
       </c>
-      <c r="M65" s="4">
-        <f t="shared" si="3"/>
-        <v>34</v>
+      <c r="M65" s="8">
+        <f t="shared" si="3"/>
+        <v>0.33779264214046822</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
@@ -3975,9 +3996,9 @@
         <f t="shared" si="2"/>
         <v>1360000</v>
       </c>
-      <c r="M66" s="4">
-        <f t="shared" si="3"/>
-        <v>1.18</v>
+      <c r="M66" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
@@ -4009,7 +4030,17 @@
         <v>138</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" ref="J67:J85" si="4">IF(ISNUMBER(SEARCH("combo", B67)), "Combo/Set", IF(ISNUMBER(SEARCH("tẩy", B67)), "Tẩy tế bào chết", IF(ISNUMBER(SEARCH("rửa mặt", B67)), "Làm sạch mặt", IF(ISNUMBER(SEARCH("tóc", B67)), "Chăm sóc tóc", IF(ISNUMBER(SEARCH("xịt khoáng", B67)), "Toner/Xịt khoáng", "Khác")))))</f>
+        <f t="shared" ref="J67:J85" si="4">IF(ISNUMBER(SEARCH("combo",B67)),"Combo/Set",
+IF(ISNUMBER(SEARCH("tẩy trang",B67)),"Tẩy trang",
+IF(OR(ISNUMBER(SEARCH("tẩy tế bào chết",B67)),ISNUMBER(SEARCH("tẩy da chết",B67))),"Tẩy tế bào chết",
+IF(ISNUMBER(SEARCH("rửa mặt",B67)),"Làm sạch mặt",
+IF(OR(ISNUMBER(SEARCH("gội",B67)),ISNUMBER(SEARCH("xả",B67)),ISNUMBER(SEARCH("tóc",B67))),"Chăm sóc tóc",
+IF(ISNUMBER(SEARCH("son dưỡng",B67)),"Chăm sóc môi",
+IF(ISNUMBER(SEARCH("chống nắng",B67)),"Chống nắng",
+IF(ISNUMBER(SEARCH("mặt nạ",B67)),"Mặt nạ",
+IF(OR(ISNUMBER(SEARCH("xịt khoáng",B67)),ISNUMBER(SEARCH("nước hoa hồng",B67)),ISNUMBER(SEARCH("nước cân bằng",B67))),"Toner/Xịt khoáng",
+IF(OR(ISNUMBER(SEARCH("tinh chất",B67)),ISNUMBER(SEARCH("kem dưỡng",B67))),"Serum/Dưỡng da",
+IF(OR(ISNUMBER(SEARCH("gel tắm",B67)),ISNUMBER(SEARCH("thâm mụn lưng",B67))),"Chăm sóc body","Khác")))))))))))</f>
         <v>Combo/Set</v>
       </c>
       <c r="K67" t="str">
@@ -4020,9 +4051,9 @@
         <f t="shared" ref="L67:L85" si="6" xml:space="preserve"> D67 * E67</f>
         <v>867890000</v>
       </c>
-      <c r="M67" s="4">
-        <f t="shared" ref="M67:M85" si="7" xml:space="preserve"> MAX(0, ROUND((1 - (F67 / L67)) * 100, 2))</f>
-        <v>61.19</v>
+      <c r="M67" s="8">
+        <f t="shared" ref="M67:M85" si="7">IF(D67&gt;C67, (D67-C67)/D67, 0)</f>
+        <v>0.61186440677966103</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
@@ -4065,9 +4096,9 @@
         <f t="shared" si="6"/>
         <v>138724000</v>
       </c>
-      <c r="M68" s="4">
+      <c r="M68" s="8">
         <f t="shared" si="7"/>
-        <v>55.72</v>
+        <v>0.55694760820045563</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
@@ -4110,9 +4141,9 @@
         <f t="shared" si="6"/>
         <v>490000</v>
       </c>
-      <c r="M69" s="4">
+      <c r="M69" s="8">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
@@ -4155,9 +4186,9 @@
         <f t="shared" si="6"/>
         <v>660000</v>
       </c>
-      <c r="M70" s="4">
+      <c r="M70" s="8">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
@@ -4200,9 +4231,9 @@
         <f t="shared" si="6"/>
         <v>3900000</v>
       </c>
-      <c r="M71" s="4">
+      <c r="M71" s="8">
         <f t="shared" si="7"/>
-        <v>22.33</v>
+        <v>0.15076923076923077</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
@@ -4235,7 +4266,7 @@
       </c>
       <c r="J72" t="str">
         <f t="shared" si="4"/>
-        <v>Tẩy tế bào chết</v>
+        <v>Tẩy trang</v>
       </c>
       <c r="K72" t="str">
         <f t="shared" si="5"/>
@@ -4245,9 +4276,9 @@
         <f t="shared" si="6"/>
         <v>14490000</v>
       </c>
-      <c r="M72" s="4">
+      <c r="M72" s="8">
         <f t="shared" si="7"/>
-        <v>28.64</v>
+        <v>0.28115942028985508</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
@@ -4290,9 +4321,9 @@
         <f t="shared" si="6"/>
         <v>76140000</v>
       </c>
-      <c r="M73" s="4">
+      <c r="M73" s="8">
         <f t="shared" si="7"/>
-        <v>50.14</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
@@ -4335,9 +4366,9 @@
         <f t="shared" si="6"/>
         <v>5735000</v>
       </c>
-      <c r="M74" s="4">
+      <c r="M74" s="8">
         <f t="shared" si="7"/>
-        <v>22.58</v>
+        <v>0.21621621621621623</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
@@ -4370,7 +4401,7 @@
       </c>
       <c r="J75" t="str">
         <f t="shared" si="4"/>
-        <v>Khác</v>
+        <v>Toner/Xịt khoáng</v>
       </c>
       <c r="K75" t="str">
         <f t="shared" si="5"/>
@@ -4380,9 +4411,9 @@
         <f t="shared" si="6"/>
         <v>4250000</v>
       </c>
-      <c r="M75" s="4">
+      <c r="M75" s="8">
         <f t="shared" si="7"/>
-        <v>25.88</v>
+        <v>0.23529411764705882</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
@@ -4415,7 +4446,7 @@
       </c>
       <c r="J76" t="str">
         <f t="shared" si="4"/>
-        <v>Khác</v>
+        <v>Chăm sóc body</v>
       </c>
       <c r="K76" t="str">
         <f t="shared" si="5"/>
@@ -4425,9 +4456,9 @@
         <f t="shared" si="6"/>
         <v>6748000</v>
       </c>
-      <c r="M76" s="4">
+      <c r="M76" s="8">
         <f t="shared" si="7"/>
-        <v>36.380000000000003</v>
+        <v>0.35269709543568467</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
@@ -4470,9 +4501,9 @@
         <f t="shared" si="6"/>
         <v>40710000</v>
       </c>
-      <c r="M77" s="4">
+      <c r="M77" s="8">
         <f t="shared" si="7"/>
-        <v>61.33</v>
+        <v>0.61186440677966103</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
@@ -4515,9 +4546,9 @@
         <f t="shared" si="6"/>
         <v>7540000</v>
       </c>
-      <c r="M78" s="4">
+      <c r="M78" s="8">
         <f t="shared" si="7"/>
-        <v>41.75</v>
+        <v>0.40689655172413791</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
@@ -4560,9 +4591,9 @@
         <f t="shared" si="6"/>
         <v>26550000</v>
       </c>
-      <c r="M79" s="4">
+      <c r="M79" s="8">
         <f t="shared" si="7"/>
-        <v>51.79</v>
+        <v>0.51355932203389831</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
@@ -4605,9 +4636,9 @@
         <f t="shared" si="6"/>
         <v>35340000</v>
       </c>
-      <c r="M80" s="4">
+      <c r="M80" s="8">
         <f t="shared" si="7"/>
-        <v>52.98</v>
+        <v>0.52631578947368418</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
@@ -4650,9 +4681,9 @@
         <f t="shared" si="6"/>
         <v>24747000</v>
       </c>
-      <c r="M81" s="4">
+      <c r="M81" s="8">
         <f t="shared" si="7"/>
-        <v>29.88</v>
+        <v>0.29203539823008851</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
@@ -4695,9 +4726,9 @@
         <f t="shared" si="6"/>
         <v>15210000</v>
       </c>
-      <c r="M82" s="4">
+      <c r="M82" s="8">
         <f t="shared" si="7"/>
-        <v>43.26</v>
+        <v>0.42564102564102563</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
@@ -4740,9 +4771,9 @@
         <f t="shared" si="6"/>
         <v>3250000</v>
       </c>
-      <c r="M83" s="4">
+      <c r="M83" s="8">
         <f t="shared" si="7"/>
-        <v>55.82</v>
+        <v>0.5476923076923077</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
@@ -4785,9 +4816,9 @@
         <f t="shared" si="6"/>
         <v>4320000</v>
       </c>
-      <c r="M84" s="4">
+      <c r="M84" s="8">
         <f t="shared" si="7"/>
-        <v>58.22</v>
+        <v>0.5083333333333333</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
@@ -4820,7 +4851,7 @@
       </c>
       <c r="J85" t="str">
         <f t="shared" si="4"/>
-        <v>Khác</v>
+        <v>Mặt nạ</v>
       </c>
       <c r="K85" t="str">
         <f t="shared" si="5"/>
@@ -4830,9 +4861,9 @@
         <f t="shared" si="6"/>
         <v>1695000</v>
       </c>
-      <c r="M85" s="4">
+      <c r="M85" s="8">
         <f t="shared" si="7"/>
-        <v>38.880000000000003</v>
+        <v>0.25073746312684364</v>
       </c>
     </row>
   </sheetData>
